--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3008-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3008-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A460CCA-BEBA-4F39-A7D4-446821FE79E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4FC3AF4-93DF-4881-A92B-52B3051A31A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{18B27D37-457B-4940-BCBD-5B15CE29B05C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6878E2F8-1375-4957-854E-B80AF6478155}"/>
   </bookViews>
   <sheets>
     <sheet name="3008-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1526,28 +1526,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F16894-45B6-4A5E-9506-22D3639F179A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D6125A-5174-4AE8-98F1-1FDCFA0E9C5B}">
   <dimension ref="A1:X41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1617,7 +1617,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1737,7 +1737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2021</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2020</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2019</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2018</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2017</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2016</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2015</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2014</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2013</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2012</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2011</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2010</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2009</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2008</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2007</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2006</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2005</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2004</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2003</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2002</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2001</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2000</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>1999</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37" t="s">
         <v>63</v>
       </c>
